--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-patient-role.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-patient-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:40+00:00</t>
+    <t>2026-04-20T06:44:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-patient-role.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-patient-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-patient-role.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-patient-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
